--- a/r5-ELGA-MOPED-335-336-Workflowstatus-Voraussetzungen-aktualisieren/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-335-336-Workflowstatus-Voraussetzungen-aktualisieren/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T10:09:42+00:00</t>
+    <t>2025-02-11T14:25:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
